--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>131090310</v>
       </c>
       <c r="B19" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>131090145</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131089521</v>
+        <v>131090275</v>
       </c>
       <c r="B28" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3585,9 +3585,14 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3596,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584995</v>
+        <v>584987</v>
       </c>
       <c r="R28" t="n">
-        <v>7060537</v>
+        <v>7060190</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3629,19 +3634,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,10 +3663,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131090275</v>
+        <v>131089521</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,16 +3674,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3697,14 +3692,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3713,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584987</v>
+        <v>584995</v>
       </c>
       <c r="R29" t="n">
-        <v>7060190</v>
+        <v>7060537</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3746,9 +3736,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R32" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,11 +4064,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4095,10 +4090,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B33" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,27 +4101,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4135,10 +4130,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R33" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4171,6 +4166,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B32" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R32" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,6 +4064,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,10 +4095,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4101,27 +4106,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R33" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4166,11 +4171,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>131090310</v>
       </c>
       <c r="B19" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>131090145</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>131090091</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>131090374</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131090601</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131090313</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>131090020</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>131090008</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>131090015</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131090275</v>
+        <v>131089521</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3585,14 +3585,9 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3601,10 +3596,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584987</v>
+        <v>584995</v>
       </c>
       <c r="R28" t="n">
-        <v>7060190</v>
+        <v>7060537</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3634,9 +3629,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131089521</v>
+        <v>131090275</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,16 +3679,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3692,9 +3697,14 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3703,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584995</v>
+        <v>584987</v>
       </c>
       <c r="R29" t="n">
-        <v>7060537</v>
+        <v>7060190</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3736,19 +3746,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,7 +3778,7 @@
         <v>131144497</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>131144494</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>131144496</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>131144498</v>
       </c>
       <c r="B33" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>131090310</v>
       </c>
       <c r="B19" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131090145</v>
+        <v>131090091</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,37 +2641,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585013</v>
+        <v>585024</v>
       </c>
       <c r="R20" t="n">
-        <v>7060142</v>
+        <v>7060099</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,22 +2735,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131090091</v>
+        <v>131090145</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,42 +2758,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585024</v>
+        <v>585013</v>
       </c>
       <c r="R21" t="n">
-        <v>7060099</v>
+        <v>7060142</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2812,7 +2817,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2822,12 +2827,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,12 +2842,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
         <v>131090374</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131090601</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131090313</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>131090020</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>131090008</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>131090015</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>131089521</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>131090275</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>131144497</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>131144494</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B32" t="n">
-        <v>57886</v>
+        <v>58046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R32" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,11 +4064,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4095,10 +4090,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B33" t="n">
-        <v>58045</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,27 +4101,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4135,10 +4130,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R33" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4171,6 +4166,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -2630,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131090091</v>
+        <v>131090145</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,42 +2641,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585024</v>
+        <v>585013</v>
       </c>
       <c r="R20" t="n">
-        <v>7060099</v>
+        <v>7060142</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2710,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,22 +2725,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131090145</v>
+        <v>131090091</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,37 +2748,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585013</v>
+        <v>585024</v>
       </c>
       <c r="R21" t="n">
-        <v>7060142</v>
+        <v>7060099</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2817,7 +2812,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2827,7 +2822,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,12 +2842,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B32" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R32" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,6 +4064,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,10 +4095,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4101,27 +4106,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R33" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4166,11 +4171,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R32" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,11 +4064,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4095,10 +4090,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B33" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,27 +4101,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4135,10 +4130,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R33" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4171,6 +4166,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>131090310</v>
       </c>
       <c r="B19" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>131090145</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>131090091</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>131090374</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131090601</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131090313</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>131090020</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>131090008</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>131090015</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131089521</v>
+        <v>131090275</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3585,9 +3585,14 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3596,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584995</v>
+        <v>584987</v>
       </c>
       <c r="R28" t="n">
-        <v>7060537</v>
+        <v>7060190</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3629,19 +3634,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,10 +3663,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131090275</v>
+        <v>131089521</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,16 +3674,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3697,14 +3692,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3713,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584987</v>
+        <v>584995</v>
       </c>
       <c r="R29" t="n">
-        <v>7060190</v>
+        <v>7060537</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3746,9 +3736,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,7 +3778,7 @@
         <v>131144497</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>131144494</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B32" t="n">
-        <v>58046</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R32" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,6 +4064,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,10 +4095,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>58047</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4101,27 +4106,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R33" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4166,11 +4171,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>131090310</v>
       </c>
       <c r="B19" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>131090145</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>131090091</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>131090374</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131090601</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131090313</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>131090020</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>131090008</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>131090015</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>131090275</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>131089521</v>
       </c>
       <c r="B29" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>131144497</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>131144494</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>131144496</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>131144498</v>
       </c>
       <c r="B33" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -3778,7 +3778,7 @@
         <v>131144497</v>
       </c>
       <c r="B30" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>131144494</v>
       </c>
       <c r="B31" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B32" t="n">
-        <v>57891</v>
+        <v>58051</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R32" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,11 +4064,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4095,10 +4090,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B33" t="n">
-        <v>58050</v>
+        <v>57892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,27 +4101,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4135,10 +4130,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R33" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4171,6 +4166,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -3988,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144498</v>
+        <v>131144496</v>
       </c>
       <c r="B32" t="n">
-        <v>58051</v>
+        <v>57892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,27 +3999,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584857</v>
+        <v>584875</v>
       </c>
       <c r="R32" t="n">
-        <v>7060494</v>
+        <v>7060422</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4064,6 +4064,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,10 +4095,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144496</v>
+        <v>131144498</v>
       </c>
       <c r="B33" t="n">
-        <v>57892</v>
+        <v>58051</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4101,27 +4106,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584875</v>
+        <v>584857</v>
       </c>
       <c r="R33" t="n">
-        <v>7060422</v>
+        <v>7060494</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4166,11 +4171,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89045182</v>
+        <v>131090310</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hållflon, SO om, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584894.9221880969</v>
+        <v>584977</v>
       </c>
       <c r="R2" t="n">
-        <v>7060194.951294071</v>
+        <v>7060194</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,48 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>olikåldrig, underväxtröjd granskog, senvuxen</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>3 substratenheter # klena granlågor av senvuxna träd</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115225950</v>
+        <v>89045182</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Hållflon, SO om, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585083</v>
+        <v>584895</v>
       </c>
       <c r="R3" t="n">
-        <v>7060029</v>
+        <v>7060195</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,31 +863,43 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>olikåldrig, underväxtröjd granskog, senvuxen</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>3 substratenheter # klena granlågor av senvuxna träd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>115223810</v>
       </c>
       <c r="B4" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,7 +927,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hållflon (Hållflon), Ång</t>
+          <t>Hållflon, Hållflon, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1023,53 +1003,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115224960</v>
+        <v>126270705</v>
       </c>
       <c r="B5" t="n">
-        <v>91121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2014</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585045</v>
+        <v>585006</v>
       </c>
       <c r="R5" t="n">
-        <v>7060179</v>
+        <v>7060536</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,12 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,77 +1086,68 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115223435</v>
+        <v>126270731</v>
       </c>
       <c r="B6" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hållflon (Hållflon), Ång</t>
+          <t>Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584880</v>
+        <v>585127</v>
       </c>
       <c r="R6" t="n">
-        <v>7060528</v>
+        <v>7060624</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,22 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,33 +1188,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115226261</v>
+        <v>115224960</v>
       </c>
       <c r="B7" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,34 +1218,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2014</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585016</v>
+        <v>585045</v>
       </c>
       <c r="R7" t="n">
-        <v>7060120</v>
+        <v>7060179</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1348,58 +1304,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115224589</v>
+        <v>126057619</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585001</v>
+        <v>585221</v>
       </c>
       <c r="R8" t="n">
-        <v>7060272</v>
+        <v>7059982</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,12 +1369,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,53 +1401,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115223499</v>
+        <v>131087388</v>
       </c>
       <c r="B9" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hållflon (Hållflon), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584861</v>
+        <v>585131</v>
       </c>
       <c r="R9" t="n">
-        <v>7060507</v>
+        <v>7060627</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,22 +1466,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,70 +1486,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115226120</v>
+        <v>131090145</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585046</v>
+        <v>585013</v>
       </c>
       <c r="R10" t="n">
-        <v>7060103</v>
+        <v>7060142</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,12 +1563,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,70 +1593,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115228303</v>
+        <v>131092646</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hållflon (Hållflon), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584998</v>
+        <v>585082</v>
       </c>
       <c r="R11" t="n">
-        <v>7060470</v>
+        <v>7060264</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,22 +1670,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,27 +1690,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115225168</v>
+        <v>115226261</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,39 +1713,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585079</v>
+        <v>585016</v>
       </c>
       <c r="R12" t="n">
-        <v>7060171</v>
+        <v>7060120</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1898,15 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115224612</v>
+        <v>126057952</v>
       </c>
       <c r="B13" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,37 +1810,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585002</v>
+        <v>585090</v>
       </c>
       <c r="R13" t="n">
-        <v>7060269</v>
+        <v>7060066</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,12 +1864,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,32 +1896,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115225979</v>
+        <v>131089521</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2041,17 +1932,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585082</v>
+        <v>584995</v>
       </c>
       <c r="R14" t="n">
-        <v>7060031</v>
+        <v>7060537</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2075,12 +1966,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,57 +2008,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118391194</v>
+        <v>115224589</v>
       </c>
       <c r="B15" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585172</v>
+        <v>585001</v>
       </c>
       <c r="R15" t="n">
-        <v>7060025</v>
+        <v>7060272</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,22 +2078,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,22 +2098,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057952</v>
+        <v>115225168</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,37 +2121,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585090</v>
+        <v>585079</v>
       </c>
       <c r="R16" t="n">
-        <v>7060066</v>
+        <v>7060171</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,12 +2180,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2212,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126059263</v>
+        <v>115225950</v>
       </c>
       <c r="B17" t="n">
-        <v>58138</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,41 +2223,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585069</v>
+        <v>585083</v>
       </c>
       <c r="R17" t="n">
-        <v>7060189</v>
+        <v>7060029</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2389,12 +2282,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,52 +2314,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126270705</v>
+        <v>115225979</v>
       </c>
       <c r="B18" t="n">
-        <v>100516</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Timmeråsen, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585006</v>
+        <v>585082</v>
       </c>
       <c r="R18" t="n">
-        <v>7060536</v>
+        <v>7060031</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2490,12 +2384,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,29 +2398,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131090310</v>
+        <v>115226120</v>
       </c>
       <c r="B19" t="n">
-        <v>91817</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,37 +2427,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584977</v>
+        <v>585046</v>
       </c>
       <c r="R19" t="n">
-        <v>7060194</v>
+        <v>7060103</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,22 +2486,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131090145</v>
+        <v>115228303</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2529,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Hållflon, Hållflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585013</v>
+        <v>584998</v>
       </c>
       <c r="R20" t="n">
-        <v>7060142</v>
+        <v>7060470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,22 +2588,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131090091</v>
+        <v>118395387</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,17 +2666,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585024</v>
+        <v>585100</v>
       </c>
       <c r="R21" t="n">
-        <v>7060099</v>
+        <v>7060200</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2807,27 +2700,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,22 +2730,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131090374</v>
+        <v>131089392</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2885,7 +2773,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2894,13 +2782,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584977</v>
+        <v>585074</v>
       </c>
       <c r="R22" t="n">
-        <v>7060203</v>
+        <v>7060648</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2929,7 +2817,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2939,12 +2827,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131090601</v>
+        <v>131089847</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,17 +2895,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hållflon, Hållflon, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584871</v>
+        <v>585024</v>
       </c>
       <c r="R23" t="n">
-        <v>7060419</v>
+        <v>7060313</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3046,7 +2934,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3056,12 +2944,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,22 +2964,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131090313</v>
+        <v>131090008</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,17 +3012,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585012</v>
+        <v>585080</v>
       </c>
       <c r="R24" t="n">
-        <v>7060182</v>
+        <v>7060076</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3163,7 +3051,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3173,12 +3061,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,22 +3081,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131090020</v>
+        <v>131090015</v>
       </c>
       <c r="B25" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3241,17 +3129,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585065</v>
+        <v>585076</v>
       </c>
       <c r="R25" t="n">
-        <v>7060076</v>
+        <v>7060075</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3280,7 +3168,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3290,12 +3178,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,22 +3198,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131090008</v>
+        <v>131090020</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,7 +3250,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585080</v>
+        <v>585065</v>
       </c>
       <c r="R26" t="n">
         <v>7060076</v>
@@ -3397,7 +3285,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3407,12 +3295,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Färska ringhack tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131090015</v>
+        <v>131090091</v>
       </c>
       <c r="B27" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,17 +3363,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Timmeråsen, Timmeråsen, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585076</v>
+        <v>585024</v>
       </c>
       <c r="R27" t="n">
-        <v>7060075</v>
+        <v>7060099</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,7 +3402,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,12 +3412,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,12 +3432,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3559,7 +3447,7 @@
         <v>131090275</v>
       </c>
       <c r="B28" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,10 +3551,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131089521</v>
+        <v>131090313</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,16 +3562,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3699,17 +3587,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584995</v>
+        <v>585012</v>
       </c>
       <c r="R29" t="n">
-        <v>7060537</v>
+        <v>7060182</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3738,7 +3626,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,7 +3636,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,22 +3656,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131144497</v>
+        <v>131090374</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,14 +3704,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Röån, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584884</v>
+        <v>584977</v>
       </c>
       <c r="R30" t="n">
-        <v>7060423</v>
+        <v>7060203</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3848,14 +3741,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3882,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131144494</v>
+        <v>131090601</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,29 +3813,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Röån, Ång</t>
+          <t>Hållflon, Hållflon, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585030</v>
+        <v>584871</v>
       </c>
       <c r="R31" t="n">
-        <v>7060258</v>
+        <v>7060419</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3959,9 +3858,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,22 +3890,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131144496</v>
+        <v>131092632</v>
       </c>
       <c r="B32" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,14 +3938,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Röån, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584875</v>
+        <v>585099</v>
       </c>
       <c r="R32" t="n">
-        <v>7060422</v>
+        <v>7060260</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4095,10 +4009,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131144498</v>
+        <v>131144494</v>
       </c>
       <c r="B33" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,27 +4020,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4135,10 +4053,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584857</v>
+        <v>585030</v>
       </c>
       <c r="R33" t="n">
-        <v>7060494</v>
+        <v>7060258</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4194,6 +4112,863 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131144496</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Röån, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>584875</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7060422</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131144497</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Röån, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>584884</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7060423</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>115223435</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hållflon, Hållflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>584880</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7060528</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126059263</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>585069</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7060189</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131144498</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Röån, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>584857</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7060494</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>115223888</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hållflon, Hållflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>584826</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7060475</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118391194</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>585172</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7060025</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126057693</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>585221</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7059982</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3367-2026 artfynd.xlsx
+++ b/artfynd/A 3367-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045182</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115223810</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270731</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115224960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057619</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131087388</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090145</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092646</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115226261</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057952</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089521</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2107,6 +2177,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115224589</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2209,6 +2284,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115225168</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2311,6 +2391,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115225950</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115225979</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2515,6 +2605,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115226120</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2627,6 +2722,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115228303</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2739,6 +2839,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395387</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2856,6 +2961,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089392</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2973,6 +3083,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089847</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3090,6 +3205,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090008</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090015</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3324,6 +3449,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090020</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3441,6 +3571,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090091</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3548,6 +3683,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090275</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3665,6 +3805,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090313</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3782,6 +3927,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090374</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3899,6 +4049,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131090601</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4006,6 +4161,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092632</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4112,6 +4272,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131144494</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4219,6 +4384,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131144496</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4326,6 +4496,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131144497</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4442,6 +4617,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115223435</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4543,6 +4723,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059263</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4645,6 +4830,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131144498</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4757,6 +4947,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115223888</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4868,6 +5063,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118391194</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4969,8 +5169,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057693</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>